--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_shapes.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_shapes.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Locations analyzed</t>
   </si>
   <si>
-    <t xml:space="preserve">Polygons defined by shapefile</t>
+    <t xml:space="preserve">Selected Locations</t>
   </si>
   <si>
     <t xml:space="preserve">Distance in miles</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">Distance type</t>
   </si>
   <si>
-    <t xml:space="preserve">Miles radius of circular buffer (or distance used if buffering around polygons)</t>
+    <t xml:space="preserve">Residents within any of the 2 specified polygons. Area in Square Miles: 3.86</t>
   </si>
   <si>
     <t xml:space="preserve">Population at x% of sites</t>
   </si>
   <si>
-    <t xml:space="preserve">0% of places account for 50% of the total population (approx.)</t>
+    <t xml:space="preserve">The most-populated 50% of the 2 places can account for at least 50% of the total population of all sites as a whole.</t>
   </si>
   <si>
     <t xml:space="preserve">Population at N sites</t>
@@ -7099,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="QY2" s="23" t="n">
-        <v>3.68793699144423</v>
+        <v>3.68793699144501</v>
       </c>
     </row>
     <row r="3">
@@ -8468,7 +8468,7 @@
         <v>136.677361809087</v>
       </c>
       <c r="QY3" s="23" t="n">
-        <v>0.176988304028012</v>
+        <v>0.176988304028013</v>
       </c>
     </row>
   </sheetData>
@@ -10295,7 +10295,7 @@
         <v>0.434667863618263</v>
       </c>
       <c r="AY2" s="28" t="n">
-        <v>0.0775605067588989</v>
+        <v>0.0775605067588988</v>
       </c>
       <c r="AZ2" s="28" t="n">
         <v>1.0786055068119</v>
@@ -10542,7 +10542,7 @@
         <v>3.61945252171656</v>
       </c>
       <c r="EF2" s="25" t="n">
-        <v>0.0861739424641989</v>
+        <v>0.086173942464199</v>
       </c>
       <c r="EG2" s="22" t="n">
         <v>30.9169599927929</v>
@@ -10563,13 +10563,13 @@
         <v>0.147347161177937</v>
       </c>
       <c r="EM2" s="23" t="n">
-        <v>0.0144567179100204</v>
+        <v>0.0144567179100203</v>
       </c>
       <c r="EN2" s="22" t="n">
         <v>7.15592219470955</v>
       </c>
       <c r="EO2" s="23" t="n">
-        <v>0.0260463744655078</v>
+        <v>0.0260463744655077</v>
       </c>
       <c r="EP2" s="22" t="n">
         <v>0</v>
@@ -11395,7 +11395,7 @@
         <v>15.036235094703</v>
       </c>
       <c r="PK2" s="25" t="n">
-        <v>16.1272574560559</v>
+        <v>16.1272574560558</v>
       </c>
       <c r="PL2" s="25" t="n">
         <v>11.8672170149733</v>
@@ -11497,7 +11497,7 @@
         <v>24.2138416096683</v>
       </c>
       <c r="QS2" s="25" t="n">
-        <v>42.5701469838121</v>
+        <v>42.570146983812</v>
       </c>
       <c r="QT2" s="25" t="n">
         <v>0</v>
@@ -11515,7 +11515,7 @@
         <v>22.4570911660588</v>
       </c>
       <c r="QY2" s="23" t="n">
-        <v>3.86492529547224</v>
+        <v>3.86492529547302</v>
       </c>
     </row>
   </sheetData>

--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_shapes.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_shapes.xlsx
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">area_sqmi</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejanalysis.com", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejanalysis.com" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">https://pedp-ejscreen.azurewebsites.net/index.html</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?shape=%7B%22type%22:%22FeatureCollection%22,%22name%22:%22shp_1%22,%22crs%22:%7B%22type%22:%22name%22,%22properties%22:%7B%22name%22:%22urn:ogc:def:crs:EPSG::4269%22%7D%7D,%22features%22:[%7B%22type%22:%22Feature%22,%22properties%22:%7B%22STATEFP%22:%2210%22,%22PLACEFP%22:%2261480%22,%22PLACENS%22:%2202389760%22,%22GEOID%22:%221061480%22,%22NAME%22:%22Riverview%22,%22NAMELSAD%22:%22RiverviewCDP%22,%22LSAD%22:%2257%22,%22CLASSFP%22:%22U1%22,%22PCICBSA%22:null,%22PCINECTA%22:null,%22MTFCC%22:%22G4210%22,%22FUNCSTAT%22:%22S%22,%22ALAND%22:9352272.0,%22AWATER%22:207421.0,%22INTPTLAT%22:%22+39.0304348%22,%22INTPTLON%22:%22-075.5186490%22,%22FIPS%22:%221061480%22,%22ejam_uniq_id%22:1,%22valid%22:true%7D,%22geometry%22:%7B%22type%22:%22Polygon%22,%22coordinates%22:[[[-75.550934,39.037819],[-75.529792,39.010917],[-75.52707,39.011546],[-75.520033,39.017339],[-75.513373,39.023808],[-75.508141,39.024679],[-75.507424,39.023393],[-75.497057,39.029215],[-75.48534,39.026936],[-75.484385,39.027727],[-75.480711,39.02753],[-75.482985,39.034257],[-75.515467,39.03991],[-75.532573,39.037128],[-75.545072,39.03926],[-75.550934,39.037819]]]%7D%7D]%7D&amp;buffer=0&amp;sitetype=shp&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.0304348,-75.518649", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?shape=%7B%22type%22:%22FeatureCollection%22,%22name%22:%22shp_1%22,%22crs%22:%7B%22type%22:%22name%22,%22properties%22:%7B%22name%22:%22urn:ogc:def:crs:EPSG::4269%22%7D%7D,%22features%22:[%7B%22type%22:%22Feature%22,%22properties%22:%7B%22STATEFP%22:%2210%22,%22PLACEFP%22:%2261480%22,%22PLACENS%22:%2202389760%22,%22GEOID%22:%221061480%22,%22NAME%22:%22Riverview%22,%22NAMELSAD%22:%22RiverviewCDP%22,%22LSAD%22:%2257%22,%22CLASSFP%22:%22U1%22,%22PCICBSA%22:null,%22PCINECTA%22:null,%22MTFCC%22:%22G4210%22,%22FUNCSTAT%22:%22S%22,%22ALAND%22:9352272.0,%22AWATER%22:207421.0,%22INTPTLAT%22:%22+39.0304348%22,%22INTPTLON%22:%22-075.5186490%22,%22FIPS%22:%221061480%22,%22ejam_uniq_id%22:1,%22valid%22:true%7D,%22geometry%22:%7B%22type%22:%22Polygon%22,%22coordinates%22:[[[-75.550934,39.037819],[-75.529792,39.010917],[-75.52707,39.011546],[-75.520033,39.017339],[-75.513373,39.023808],[-75.508141,39.024679],[-75.507424,39.023393],[-75.497057,39.029215],[-75.48534,39.026936],[-75.484385,39.027727],[-75.480711,39.02753],[-75.482985,39.034257],[-75.515467,39.03991],[-75.532573,39.037128],[-75.545072,39.03926],[-75.550934,39.037819]]]%7D%7D]%7D&amp;buffer=0&amp;sitetype=shp&amp;validate_regids=FALSE" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.0304348,-75.518649" target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">DE</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">Delaware</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?shape=%7B%22type%22:%22FeatureCollection%22,%22name%22:%22shp_2%22,%22crs%22:%7B%22type%22:%22name%22,%22properties%22:%7B%22name%22:%22urn:ogc:def:crs:EPSG::4269%22%7D%7D,%22features%22:[%7B%22type%22:%22Feature%22,%22properties%22:%7B%22STATEFP%22:%2210%22,%22PLACEFP%22:%2274330%22,%22PLACENS%22:%2202391463%22,%22GEOID%22:%221074330%22,%22NAME%22:%22Viola%22,%22NAMELSAD%22:%22Violatown%22,%22LSAD%22:%2243%22,%22CLASSFP%22:%22C1%22,%22PCICBSA%22:null,%22PCINECTA%22:null,%22MTFCC%22:%22G4110%22,%22FUNCSTAT%22:%22A%22,%22ALAND%22:458783.0,%22AWATER%22:0.0,%22INTPTLAT%22:%22+39.0429304%22,%22INTPTLON%22:%22-075.5714580%22,%22FIPS%22:%221074330%22,%22ejam_uniq_id%22:2,%22valid%22:true%7D,%22geometry%22:%7B%22type%22:%22Polygon%22,%22coordinates%22:[[[-75.575863,39.041496],[-75.574359,39.04037],[-75.567422,39.03991],[-75.566825,39.044623],[-75.575399,39.045981],[-75.575863,39.041496]]]%7D%7D]%7D&amp;buffer=0&amp;sitetype=shp&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.0429304,-75.571458", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?shape=%7B%22type%22:%22FeatureCollection%22,%22name%22:%22shp_2%22,%22crs%22:%7B%22type%22:%22name%22,%22properties%22:%7B%22name%22:%22urn:ogc:def:crs:EPSG::4269%22%7D%7D,%22features%22:[%7B%22type%22:%22Feature%22,%22properties%22:%7B%22STATEFP%22:%2210%22,%22PLACEFP%22:%2274330%22,%22PLACENS%22:%2202391463%22,%22GEOID%22:%221074330%22,%22NAME%22:%22Viola%22,%22NAMELSAD%22:%22Violatown%22,%22LSAD%22:%2243%22,%22CLASSFP%22:%22C1%22,%22PCICBSA%22:null,%22PCINECTA%22:null,%22MTFCC%22:%22G4110%22,%22FUNCSTAT%22:%22A%22,%22ALAND%22:458783.0,%22AWATER%22:0.0,%22INTPTLAT%22:%22+39.0429304%22,%22INTPTLON%22:%22-075.5714580%22,%22FIPS%22:%221074330%22,%22ejam_uniq_id%22:2,%22valid%22:true%7D,%22geometry%22:%7B%22type%22:%22Polygon%22,%22coordinates%22:[[[-75.575863,39.041496],[-75.574359,39.04037],[-75.567422,39.03991],[-75.566825,39.044623],[-75.575399,39.045981],[-75.575863,39.041496]]]%7D%7D]%7D&amp;buffer=0&amp;sitetype=shp&amp;validate_regids=FALSE" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.0429304,-75.571458" target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">value</t>

--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_shapes.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_shapes.xlsx
@@ -4897,8 +4897,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="11">
-    <numFmt numFmtId="167" formatCode="#,###,###"/>
+  <numFmts count="12">
+    <numFmt numFmtId="168" formatCode="#,###,###"/>
     <numFmt numFmtId="169" formatCode="#,###,##0.0"/>
     <numFmt numFmtId="171" formatCode="#,###,##0.00"/>
     <numFmt numFmtId="172" formatCode="#,###,##0.000"/>
@@ -4907,8 +4907,9 @@
     <numFmt numFmtId="175" formatCode="#,##0.0"/>
     <numFmt numFmtId="176" formatCode="#0"/>
     <numFmt numFmtId="177" formatCode="0%"/>
-    <numFmt numFmtId="178" formatCode="#,###,###"/>
-    <numFmt numFmtId="179" formatCode="$#,##0"/>
+    <numFmt numFmtId="178" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="179" formatCode="#,###,###"/>
+    <numFmt numFmtId="180" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -5066,7 +5067,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5138,7 +5139,7 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -5149,6 +5150,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7896,7 +7898,7 @@
         <v>1</v>
       </c>
       <c r="E2"/>
-      <c r="F2" s="34" t="n">
+      <c r="F2" s="35" t="n">
         <v>2209.8</v>
       </c>
       <c r="G2"/>
@@ -8362,7 +8364,7 @@
       <c r="FK2" s="33" t="n">
         <v>0.539989217626338</v>
       </c>
-      <c r="FL2" s="35" t="n">
+      <c r="FL2" s="36" t="n">
         <v>41213.5462555956</v>
       </c>
       <c r="FM2" s="33" t="n">
@@ -8435,13 +8437,13 @@
       <c r="GL2" s="33" t="n">
         <v>0.204102564102564</v>
       </c>
-      <c r="GM2" s="33" t="n">
+      <c r="GM2" s="34" t="n">
         <v>5.6</v>
       </c>
-      <c r="GN2" s="27" t="n">
+      <c r="GN2" s="34" t="n">
         <v>11.1</v>
       </c>
-      <c r="GO2" s="27" t="n">
+      <c r="GO2" s="34" t="n">
         <v>6.6</v>
       </c>
       <c r="GP2" s="25" t="n">
@@ -8852,13 +8854,13 @@
       <c r="LU2" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV2" s="33" t="n">
+      <c r="LV2" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW2" s="25" t="n">
+      <c r="LW2" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX2" s="26" t="n">
+      <c r="LX2" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY2" s="33" t="n">
@@ -8969,13 +8971,13 @@
       <c r="NH2" s="33" t="n">
         <v>0.200285162865808</v>
       </c>
-      <c r="NI2" s="33" t="n">
+      <c r="NI2" s="34" t="n">
         <v>5.92225392296719</v>
       </c>
-      <c r="NJ2" s="26" t="n">
+      <c r="NJ2" s="34" t="n">
         <v>10.3305278174037</v>
       </c>
-      <c r="NK2" s="26" t="n">
+      <c r="NK2" s="34" t="n">
         <v>7.00927246790299</v>
       </c>
       <c r="NL2" s="33" t="n">
@@ -9901,7 +9903,7 @@
         <v>1</v>
       </c>
       <c r="E3"/>
-      <c r="F3" s="34" t="n">
+      <c r="F3" s="35" t="n">
         <v>147.7</v>
       </c>
       <c r="G3"/>
@@ -10367,7 +10369,7 @@
       <c r="FK3" s="33" t="n">
         <v>0.489577129243597</v>
       </c>
-      <c r="FL3" s="35" t="n">
+      <c r="FL3" s="36" t="n">
         <v>29974</v>
       </c>
       <c r="FM3" s="33" t="n">
@@ -10440,13 +10442,13 @@
       <c r="GL3" s="33" t="n">
         <v>0.231794871794872</v>
       </c>
-      <c r="GM3" s="33" t="n">
+      <c r="GM3" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="GN3" s="27" t="n">
+      <c r="GN3" s="34" t="n">
         <v>11.1</v>
       </c>
-      <c r="GO3" s="27" t="n">
+      <c r="GO3" s="34" t="n">
         <v>7.4</v>
       </c>
       <c r="GP3" s="25" t="n">
@@ -10857,13 +10859,13 @@
       <c r="LU3" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV3" s="33" t="n">
+      <c r="LV3" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW3" s="25" t="n">
+      <c r="LW3" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX3" s="26" t="n">
+      <c r="LX3" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY3" s="33" t="n">
@@ -10974,13 +10976,13 @@
       <c r="NH3" s="33" t="n">
         <v>0.200285162865808</v>
       </c>
-      <c r="NI3" s="33" t="n">
+      <c r="NI3" s="34" t="n">
         <v>5.92225392296719</v>
       </c>
-      <c r="NJ3" s="26" t="n">
+      <c r="NJ3" s="34" t="n">
         <v>10.3305278174037</v>
       </c>
-      <c r="NK3" s="26" t="n">
+      <c r="NK3" s="34" t="n">
         <v>7.00927246790299</v>
       </c>
       <c r="NL3" s="33" t="n">
@@ -14997,7 +14999,7 @@
       <c r="E2" t="s">
         <v>728</v>
       </c>
-      <c r="F2" s="34" t="n">
+      <c r="F2" s="35" t="n">
         <v>2357.5</v>
       </c>
       <c r="G2"/>
@@ -15457,7 +15459,7 @@
       <c r="FK2" s="33" t="n">
         <v>0.536831878531257</v>
       </c>
-      <c r="FL2" s="35" t="n">
+      <c r="FL2" s="36" t="n">
         <v>40509.6067850793</v>
       </c>
       <c r="FM2" s="33" t="n">
@@ -15530,13 +15532,13 @@
       <c r="GL2" s="33" t="n">
         <v>0.205836949812716</v>
       </c>
-      <c r="GM2" s="33" t="n">
+      <c r="GM2" s="34" t="n">
         <v>5.68768283312434</v>
       </c>
-      <c r="GN2" s="27" t="n">
+      <c r="GN2" s="34" t="n">
         <v>11.1</v>
       </c>
-      <c r="GO2" s="27" t="n">
+      <c r="GO2" s="34" t="n">
         <v>6.65010447607105</v>
       </c>
       <c r="GP2" s="25" t="n">
@@ -15947,13 +15949,13 @@
       <c r="LU2" s="33" t="n">
         <v>0.195319647024096</v>
       </c>
-      <c r="LV2" s="33" t="n">
+      <c r="LV2" s="34" t="n">
         <v>5.78866112415659</v>
       </c>
-      <c r="LW2" s="25" t="n">
+      <c r="LW2" s="34" t="n">
         <v>10.3142467897866</v>
       </c>
-      <c r="LX2" s="26" t="n">
+      <c r="LX2" s="34" t="n">
         <v>6.44134924160715</v>
       </c>
       <c r="LY2" s="33" t="n">
@@ -16064,13 +16066,13 @@
       <c r="NH2" s="33" t="n">
         <v>0.200285162865808</v>
       </c>
-      <c r="NI2" s="33" t="n">
+      <c r="NI2" s="34" t="n">
         <v>5.92225392296719</v>
       </c>
-      <c r="NJ2" s="26" t="n">
+      <c r="NJ2" s="34" t="n">
         <v>10.3305278174037</v>
       </c>
-      <c r="NK2" s="26" t="n">
+      <c r="NK2" s="34" t="n">
         <v>7.00927246790299</v>
       </c>
       <c r="NL2" s="33" t="n">

--- a/inst/testdata/examples_of_output/testoutput_ejam2excel_shapes.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejam2excel_shapes.xlsx
@@ -4898,18 +4898,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="12">
-    <numFmt numFmtId="168" formatCode="#,###,###"/>
-    <numFmt numFmtId="169" formatCode="#,###,##0.0"/>
-    <numFmt numFmtId="171" formatCode="#,###,##0.00"/>
-    <numFmt numFmtId="172" formatCode="#,###,##0.000"/>
+    <numFmt numFmtId="167" formatCode="#,###,###"/>
+    <numFmt numFmtId="168" formatCode="#,###,##0.0"/>
+    <numFmt numFmtId="170" formatCode="#,###,##0.00"/>
+    <numFmt numFmtId="171" formatCode="#,###,##0.000"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00"/>
     <numFmt numFmtId="173" formatCode="#,##0.00"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00"/>
-    <numFmt numFmtId="175" formatCode="#,##0.0"/>
-    <numFmt numFmtId="176" formatCode="#0"/>
-    <numFmt numFmtId="177" formatCode="0%"/>
-    <numFmt numFmtId="178" formatCode="0&quot;%&quot;"/>
-    <numFmt numFmtId="179" formatCode="#,###,###"/>
-    <numFmt numFmtId="180" formatCode="$#,##0"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0"/>
+    <numFmt numFmtId="175" formatCode="#0"/>
+    <numFmt numFmtId="176" formatCode="0%"/>
+    <numFmt numFmtId="177" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="178" formatCode="#,###,###"/>
+    <numFmt numFmtId="179" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -5139,8 +5139,9 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -5150,7 +5151,6 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
